--- a/public/assets/workplan_template.xlsx
+++ b/public/assets/workplan_template.xlsx
@@ -340,7 +340,7 @@
     <t>2026/07/31</t>
   </si>
   <si>
-    <t>إطلاق الدفعة الأولى</t>
+    <t>إطلاق المرحلة الأولى</t>
   </si>
   <si>
     <t>يوليو – نوفمبر 2026</t>
@@ -355,7 +355,7 @@
     <t>2026/11/30</t>
   </si>
   <si>
-    <t>إطلاق الدفعة الثانية</t>
+    <t>إطلاق المرحلة الثانية</t>
   </si>
   <si>
     <t>ديسمبر 2026 – فبراير 2027</t>
@@ -370,7 +370,7 @@
     <t>2027/02/28</t>
   </si>
   <si>
-    <t>إطلاق الدفعة الثالثة</t>
+    <t>إطلاق المرحلة الثالثة</t>
   </si>
   <si>
     <t>مارس – مايو 2027</t>
@@ -385,7 +385,7 @@
     <t>2027/05/31</t>
   </si>
   <si>
-    <t>إطلاق الدفعة الرابعة</t>
+    <t>إطلاق المرحلة الرابعة</t>
   </si>
   <si>
     <t>يونيو – أغسطس 2027</t>
